--- a/example data/25mm/Results/ID 18 - Run 2/ID 18 - Run 2 - Standard Devs. Stepcycle.xlsx
+++ b/example data/25mm/Results/ID 18 - Run 2/ID 18 - Run 2 - Standard Devs. Stepcycle.xlsx
@@ -425,181 +425,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SC Percentages</t>
+          <t>SC Percentage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nose x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nose y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ear base x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ear base y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Front paw tao x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Front paw tao y</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wrist x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wrist y</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elbow x</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Elbow y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Shoulder x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lower Shoulder y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Shoulder x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upper Shoulder y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Iliac Crest y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Hip x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Hip y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Knee x</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Knee y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle x</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ankle y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao x</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hind paw tao y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tail base x</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Tail base y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tail center x</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tail center y</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tail tip x</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Tail tip y</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Velocity</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Acceleration</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Velocity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Acceleration</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Velocity</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Acceleration</t>
         </is>
@@ -610,106 +685,151 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8225109471591561</v>
+        <v>5.173053091176298</v>
       </c>
       <c r="C2" t="n">
-        <v>1.180631093972782</v>
+        <v>0.8225109471591501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2922567693360523</v>
+        <v>4.429936761847435</v>
       </c>
       <c r="E2" t="n">
-        <v>1.105737971333194</v>
+        <v>1.18063109397278</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34981130156999</v>
+        <v>9.530688017500777</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6128874998762077</v>
+        <v>0.2922567693360602</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3360441988213436</v>
+        <v>8.765613083456525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8317722571000015</v>
+        <v>1.105737971333204</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7720737337429822</v>
+        <v>7.800063239933504</v>
       </c>
       <c r="K2" t="n">
-        <v>1.707279198709047</v>
+        <v>1.349811301569996</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9573298044317942</v>
+        <v>6.561065796965519</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5566498984563409</v>
+        <v>0.6128874998762198</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5236282553249064</v>
+        <v>6.483488014265375</v>
       </c>
       <c r="O2" t="n">
+        <v>0.3360441988213508</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.020296928698403</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8317722571000054</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.13908003869834</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7720737337429898</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.618997138539232</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.707279198709048</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.562947359153296</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9573298044317844</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3969584202295573</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.556649898456344</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5.484540404732286</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.523628255324903</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.84136088915488</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.777168113861824</v>
       </c>
-      <c r="P2" t="n">
-        <v>6.39737970924916</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7.989902461682772</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.93465635650488</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10.58728400966519</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="AD2" t="n">
+        <v>64.29854780797363</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6.397379709249156</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.1979508008787771</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>0.0394889386550941</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>0.1870564280433841</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>0.2093946646683139</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>0.3295792331281499</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AK2" t="n">
         <v>0.3511947981369979</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AL2" t="n">
         <v>0.4047608515932527</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AM2" t="n">
         <v>0.4062017278081927</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AN2" t="n">
         <v>0.2483225449889021</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AO2" t="n">
         <v>0.2581364643994319</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1.789494902555522</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.7868464947226477</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.7802664265490967</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AP2" t="n">
+        <v>7.98990246168281</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.934656356504873</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.58728400966517</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.789494902555527</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.7868464947226802</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.7802664265490704</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1.028871191404119</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AW2" t="n">
         <v>1.181594362073254</v>
       </c>
-      <c r="AI2" t="n">
-        <v>1.643726835411553</v>
+      <c r="AX2" t="n">
+        <v>1.643726835411573</v>
       </c>
     </row>
     <row r="3">
@@ -717,106 +837,151 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9476950115197129</v>
+        <v>5.373058787222138</v>
       </c>
       <c r="C3" t="n">
-        <v>1.103740600667619</v>
+        <v>0.9476950115197086</v>
       </c>
       <c r="D3" t="n">
-        <v>1.626900522756096</v>
+        <v>4.425742018497267</v>
       </c>
       <c r="E3" t="n">
-        <v>1.443790660912749</v>
+        <v>1.103740600667612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8870187414341044</v>
+        <v>6.968413027191163</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5377683334653254</v>
+        <v>1.626900522756095</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4792845673281735</v>
+        <v>6.777266117586912</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7432260094875979</v>
+        <v>1.443790660912744</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9436666901691374</v>
+        <v>6.937673370566045</v>
       </c>
       <c r="K3" t="n">
-        <v>1.711802940121274</v>
+        <v>0.8870187414341049</v>
       </c>
       <c r="L3" t="n">
-        <v>1.177510816353839</v>
+        <v>6.154047031520243</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3562731301283998</v>
+        <v>0.5377683334653298</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000842352579628</v>
+        <v>6.211690429938606</v>
       </c>
       <c r="O3" t="n">
-        <v>3.66060298967088</v>
+        <v>0.4792845673281692</v>
       </c>
       <c r="P3" t="n">
+        <v>4.087862081032306</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7432260094875862</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.280572689249031</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9436666901691328</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.856037220939244</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.711802940121266</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.005832962742225</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.177510816353848</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.1851659858397772</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3562731301284039</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.110279666530522</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000842352579622</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.631961278461613</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.660602989670886</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>67.2783875141326</v>
+      </c>
+      <c r="AE3" t="n">
         <v>10.14523168147246</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.854389598065963</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5.502640997932776</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="AF3" t="n">
+        <v>0.2437006636512296</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.1037513735914007</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1774073304118113</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.04333112307201553</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2430699484844368</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.07962753460601965</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.3424995102202986</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.1525777559570644</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.2910217730055546</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.1416828789261361</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.854389598065948</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.502640997932795</v>
+      </c>
+      <c r="AR3" t="n">
         <v>10.89270763880957</v>
       </c>
-      <c r="T3" t="n">
-        <v>0.2437006636512296</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1037513735914007</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1774073304118113</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.04333112307201553</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.2430699484844368</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.07962753460601965</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.3424995102202986</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.1525777559570644</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.2910217730055546</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.1416828789261361</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.934198229062364</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.3480022576256553</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.7441767311933696</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.7472375787657832</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.279036892127695</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.6801892069403038</v>
+      <c r="AS3" t="n">
+        <v>1.934198229062374</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.3480022576256575</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.744176731193377</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.7472375787657932</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.279036892127708</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.6801892069402949</v>
       </c>
     </row>
     <row r="4">
@@ -824,106 +989,151 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6072165822914581</v>
+        <v>5.517529040014069</v>
       </c>
       <c r="C4" t="n">
-        <v>1.08885540396224</v>
+        <v>0.6072165822914537</v>
       </c>
       <c r="D4" t="n">
-        <v>1.809766462740982</v>
+        <v>4.59718481517407</v>
       </c>
       <c r="E4" t="n">
-        <v>1.645275152469398</v>
+        <v>1.088855403962242</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5794487407759894</v>
+        <v>4.577845716553991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8626729978309472</v>
+        <v>1.809766462740992</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8649332898926012</v>
+        <v>4.596765001495564</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5065479715830294</v>
+        <v>1.645275152469404</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5489454839442234</v>
+        <v>5.450131615546522</v>
       </c>
       <c r="K4" t="n">
-        <v>1.424134489183591</v>
+        <v>0.5794487407759933</v>
       </c>
       <c r="L4" t="n">
-        <v>1.759513144951852</v>
+        <v>5.340876592192979</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3946217824530412</v>
+        <v>0.8626729978309559</v>
       </c>
       <c r="N4" t="n">
-        <v>1.194274240449733</v>
+        <v>5.448850077199637</v>
       </c>
       <c r="O4" t="n">
+        <v>0.8649332898925987</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.588162664534632</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5065479715830379</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.779810650836387</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5489454839442227</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.039364423398151</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.424134489183598</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.199665039363297</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.75951314495185</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3784397914891525</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3946217824530377</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.663489070707532</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.194274240449737</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.027329309107891</v>
+      </c>
+      <c r="AC4" t="n">
         <v>3.651958424117316</v>
       </c>
-      <c r="P4" t="n">
-        <v>17.52878126309042</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.932501567482739</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.269394222632943</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AD4" t="n">
+        <v>69.13553834001654</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17.52878126309043</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.07410999979433017</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1364121079858747</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2356585965062027</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.148979245329591</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1980509319160468</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.09259304525561038</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3192888256338461</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.08368600869252477</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2057798870495225</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1417378052394026</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.932501567482752</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.269394222632951</v>
+      </c>
+      <c r="AR4" t="n">
         <v>13.18857960956388</v>
       </c>
-      <c r="T4" t="n">
-        <v>0.07410999979433017</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1364121079858747</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.2356585965062027</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.148979245329591</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.1980509319160468</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.09259304525561038</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.3192888256338461</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.08368600869252477</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.2057798870495225</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.1417378052394026</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.592917199947087</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.8476329699133618</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.576778305859909</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.8300157641893967</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.193611545863372</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.4020756128321722</v>
+      <c r="AS4" t="n">
+        <v>2.592917199947093</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.8476329699133623</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.576778305859926</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8300157641893902</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.193611545863363</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.4020756128321619</v>
       </c>
     </row>
     <row r="5">
@@ -931,106 +1141,151 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2196746706939252</v>
+        <v>5.435887477011548</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5146151828868171</v>
+        <v>0.2196746706939266</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9056986654538166</v>
+        <v>4.661825869355465</v>
       </c>
       <c r="E5" t="n">
-        <v>0.740191338376388</v>
+        <v>0.5146151828868188</v>
       </c>
       <c r="F5" t="n">
-        <v>1.449599069974141</v>
+        <v>2.483987212485133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8270051450879347</v>
+        <v>0.9056986654538149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7635014292121305</v>
+        <v>2.485703246528228</v>
       </c>
       <c r="I5" t="n">
-        <v>0.29317932084527</v>
+        <v>0.7401913383763959</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2481427171237929</v>
+        <v>3.505753023572526</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8319621809169994</v>
+        <v>1.449599069974136</v>
       </c>
       <c r="L5" t="n">
-        <v>1.517703201644466</v>
+        <v>4.105832432904973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5462421782021093</v>
+        <v>0.8270051450879352</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8104027368484594</v>
+        <v>4.695420876396025</v>
       </c>
       <c r="O5" t="n">
-        <v>2.881452780802324</v>
+        <v>0.7635014292121273</v>
       </c>
       <c r="P5" t="n">
-        <v>10.17016644646545</v>
+        <v>5.033871696778705</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.139258689988728</v>
+        <v>0.2931793208452632</v>
       </c>
       <c r="R5" t="n">
-        <v>2.320132796427587</v>
+        <v>5.264155286471073</v>
       </c>
       <c r="S5" t="n">
-        <v>14.00761593310774</v>
+        <v>0.2481427171237891</v>
       </c>
       <c r="T5" t="n">
+        <v>3.300541640459091</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.8319621809169987</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.908766620546211</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.517703201644469</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.376478814739826</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5462421782021105</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.717427563395709</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.8104027368484565</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.370160787114946</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.881452780802315</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>35.10402060465107</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>10.17016644646544</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0.08551418724279417</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>0.06848526597123106</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>0.3873686402284975</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AI5" t="n">
         <v>0.1016427997604161</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AJ5" t="n">
         <v>0.1120075918781141</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
         <v>0.1165427426938579</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>0.2047626690194767</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AM5" t="n">
         <v>0.1532854830770819</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
         <v>0.3444707794348609</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AO5" t="n">
         <v>0.07836152357854438</v>
       </c>
-      <c r="AD5" t="n">
-        <v>4.309210525960006</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.5656988940389192</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3.060136955644572</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.5300116933045519</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.313778479355968</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.660053562673099</v>
+      <c r="AP5" t="n">
+        <v>7.139258689988718</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.320132796427604</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14.00761593310778</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.309210525959999</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.5656988940389215</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.060136955644569</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.5300116933045552</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.313778479355956</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.66005356267311</v>
       </c>
     </row>
     <row r="6">
@@ -1038,106 +1293,151 @@
         <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2255229880063502</v>
+        <v>5.740496314120125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4096413778026999</v>
+        <v>0.2255229880063477</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5455219895405006</v>
+        <v>4.8418325172106</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1895054947044148</v>
+        <v>0.4096413778027063</v>
       </c>
       <c r="F6" t="n">
-        <v>1.454663597304213</v>
+        <v>1.745190219522792</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9567418835511917</v>
+        <v>0.5455219895405016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6563528242624048</v>
+        <v>1.516648163227774</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5012117883100782</v>
+        <v>0.1895054947044174</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4311904060622813</v>
+        <v>3.318648189789476</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5004225131059279</v>
+        <v>1.454663597304215</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8311177825124627</v>
+        <v>3.736788675212384</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3571017629280662</v>
+        <v>0.9567418835512015</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7610392304020487</v>
+        <v>4.469382471906437</v>
       </c>
       <c r="O6" t="n">
-        <v>2.677383096884448</v>
+        <v>0.656352824262419</v>
       </c>
       <c r="P6" t="n">
-        <v>5.2465361714074</v>
+        <v>5.381073622558447</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.84410973803928</v>
+        <v>0.5012117883100726</v>
       </c>
       <c r="R6" t="n">
-        <v>8.11389425540378</v>
+        <v>5.292182029333927</v>
       </c>
       <c r="S6" t="n">
+        <v>0.4311904060622806</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.207500196005121</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5004225131059254</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.272508760496875</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8311177825124589</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.2015642406090477</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3571017629280649</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.286241523275727</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.7610392304020455</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.439189908298496</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.677383096884442</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>21.48205059290129</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5.246536171407394</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.3070701860841923</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.1777654342849797</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3320801789457306</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4222322143385688</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2430004361956415</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.4905052930262444</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.03217623793551023</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1119526561102057</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1852906204018227</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1072703119166809</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12.84410973803931</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.113894255403824</v>
+      </c>
+      <c r="AR6" t="n">
         <v>12.57233861059128</v>
       </c>
-      <c r="T6" t="n">
-        <v>0.3070701860841923</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1777654342849797</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.3320801789457306</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.4222322143385688</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.2430004361956415</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4905052930262444</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.03217623793551023</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.1119526561102057</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.1852906204018227</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.1072703119166809</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.453577052423885</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.9827310775820794</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.3798384076748669</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.074426999682006</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.063238574959723</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.208720808864359</v>
+      <c r="AS6" t="n">
+        <v>1.453577052423912</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.9827310775820812</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.379838407674877</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.074426999682014</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.06323857495973</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.208720808864355</v>
       </c>
     </row>
     <row r="7">
@@ -1145,106 +1445,151 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1685922865898973</v>
+        <v>5.836541910650969</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3883056651184859</v>
+        <v>0.1685922865899063</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5438203194128872</v>
+        <v>4.536884780916453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3459892436305392</v>
+        <v>0.3883056651184839</v>
       </c>
       <c r="F7" t="n">
-        <v>1.419572050346004</v>
+        <v>1.771455168543582</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8909738600857927</v>
+        <v>0.5438203194128863</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6274576876263996</v>
+        <v>1.176923820284859</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3747769725806861</v>
+        <v>0.3459892436305416</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5212295871988933</v>
+        <v>3.041554971606108</v>
       </c>
       <c r="K7" t="n">
-        <v>0.845308696338339</v>
+        <v>1.419572050346006</v>
       </c>
       <c r="L7" t="n">
-        <v>1.405729069011417</v>
+        <v>3.551554099692167</v>
       </c>
       <c r="M7" t="n">
-        <v>1.498199435139512</v>
+        <v>0.8909738600857972</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6320101586950546</v>
+        <v>4.114316994067522</v>
       </c>
       <c r="O7" t="n">
-        <v>2.198127060443841</v>
+        <v>0.6274576876264039</v>
       </c>
       <c r="P7" t="n">
-        <v>4.694073478725169</v>
+        <v>5.449950003878167</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.6290699315058</v>
+        <v>0.3747769725806895</v>
       </c>
       <c r="R7" t="n">
-        <v>2.481784081430818</v>
+        <v>5.494454543714911</v>
       </c>
       <c r="S7" t="n">
-        <v>4.52470658525942</v>
+        <v>0.5212295871988909</v>
       </c>
       <c r="T7" t="n">
+        <v>5.114224594716253</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.8453086963383399</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.92792005608645</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.405729069011404</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.065696808160079</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.498199435139501</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.915387893693275</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.6320101586950532</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.22764547306791</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.198127060443846</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>20.27220884014862</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4.694073478725175</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.14934916041452</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>0.8578682228351653</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>1.171304328724475</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>0.1370692648943899</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AJ7" t="n">
         <v>1.634960720796135</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AK7" t="n">
         <v>0.2409299779914771</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AL7" t="n">
         <v>0.1625121106600934</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AM7" t="n">
         <v>0.02026948911940155</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AN7" t="n">
         <v>0.06928368381079264</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AO7" t="n">
         <v>0.1545625344236644</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0.3595041589930159</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>4.32272989826194</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>9.412604964010736</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.761637041192238</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>10.12251576911367</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.301432851678223</v>
+      <c r="AP7" t="n">
+        <v>17.62906993150586</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.481784081430797</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.524706585259432</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.3595041589930139</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.322729898261951</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.412604964010747</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.761637041192244</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10.12251576911369</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.301432851678218</v>
       </c>
     </row>
     <row r="8">
@@ -1252,106 +1597,151 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>0.289080340450652</v>
+        <v>5.326186313450932</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2961767990185581</v>
+        <v>0.2890803404506538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5188854775776496</v>
+        <v>4.046518407216445</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2012743636618591</v>
+        <v>0.2961767990185648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7861779697004586</v>
+        <v>1.961421001443622</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3592421470229146</v>
+        <v>0.5188854775776468</v>
       </c>
       <c r="H8" t="n">
-        <v>0.167999377916672</v>
+        <v>1.156046414756085</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2845167568668787</v>
+        <v>0.2012743636618584</v>
       </c>
       <c r="J8" t="n">
-        <v>1.116769258479535</v>
+        <v>2.95899404267547</v>
       </c>
       <c r="K8" t="n">
+        <v>0.7861779697004643</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.070906924799697</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.35924214702292</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.493689364373489</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1679993779166786</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.227360677354697</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2845167568668679</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.463327864063201</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.116769258479529</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7.632220153776236</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.98915645508145</v>
       </c>
-      <c r="L8" t="n">
-        <v>2.950369770630293</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.521036384481383</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.2877924362917432</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.644059218816814</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.933963256462235</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10.47426486718891</v>
-      </c>
-      <c r="R8" t="n">
-        <v>17.64914796321689</v>
-      </c>
-      <c r="S8" t="n">
-        <v>16.52135720612421</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
+        <v>6.501147713130725</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.950369770630285</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.888631167574061</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.521036384481382</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.492325775536866</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2877924362917361</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.259556412483334</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.644059218816817</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19.1969621485455</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.93396325646224</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.851643375712662</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>0.9621141155848484</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>1.166986890079337</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AI8" t="n">
         <v>0.09445910543806893</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AJ8" t="n">
         <v>1.131032567554999</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>0.5366785900076415</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AL8" t="n">
         <v>0.03931676806266842</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AM8" t="n">
         <v>0.02858408703924126</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AN8" t="n">
         <v>0.1312931408943627</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AO8" t="n">
         <v>0.06164932595161582</v>
       </c>
-      <c r="AD8" t="n">
-        <v>8.831884980808674</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3.060668936006589</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>5.99527271363491</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.96472105304393</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>8.24376181254758</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3.601612052670947</v>
+      <c r="AP8" t="n">
+        <v>10.47426486718897</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17.64914796321688</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16.52135720612426</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.831884980808686</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.060668936006608</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.995272713634905</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.964721053043935</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.243761812547568</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.601612052670982</v>
       </c>
     </row>
     <row r="9">
@@ -1359,106 +1749,151 @@
         <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>0.545327622506437</v>
+        <v>4.769075866751171</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5346174736699182</v>
+        <v>0.5453276225064387</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6724692890334291</v>
+        <v>3.267260668595815</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3433922429109733</v>
+        <v>0.5346174736699176</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8635885805751301</v>
+        <v>2.170482768468792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5883504570643308</v>
+        <v>0.6724692890334261</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3814498744235275</v>
+        <v>1.182508616900248</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5308803156042731</v>
+        <v>0.3433922429109726</v>
       </c>
       <c r="J9" t="n">
-        <v>1.591607325057676</v>
+        <v>2.841105682355904</v>
       </c>
       <c r="K9" t="n">
-        <v>2.758240455729356</v>
+        <v>0.8635885805751273</v>
       </c>
       <c r="L9" t="n">
-        <v>3.006341644087205</v>
+        <v>2.978985579197657</v>
       </c>
       <c r="M9" t="n">
-        <v>2.338974138214334</v>
+        <v>0.5883504570643342</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1941882888833625</v>
+        <v>3.30464639072683</v>
       </c>
       <c r="O9" t="n">
+        <v>0.3814498744235317</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.380396560178224</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5308803156042751</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.102195938422035</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.591607325057679</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8.20537106858745</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.758240455729357</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.518701118064302</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.006341644087199</v>
+      </c>
+      <c r="X9" t="n">
+        <v>7.30927689106676</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.338974138214338</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.835101273396251</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.1941882888833597</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.520139067664424</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.420494136841019</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.654644826781961</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.955497276736586</v>
-      </c>
-      <c r="R9" t="n">
-        <v>20.5536445212653</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25.3876133947295</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="AD9" t="n">
+        <v>18.65586634758434</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.654644826781955</v>
+      </c>
+      <c r="AF9" t="n">
         <v>3.557978062023488</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>0.04847706881530584</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>1.047394585642811</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>0.1606450188651613</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>0.7906075925877343</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0.2630622085641557</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AK9" t="n">
+        <v>0.2630622085641553</v>
+      </c>
+      <c r="AL9" t="n">
         <v>0.1723597676538544</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AM9" t="n">
         <v>0.03604278072858543</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AN9" t="n">
         <v>0.1341935449191557</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AO9" t="n">
         <v>0.3383256466117907</v>
       </c>
-      <c r="AD9" t="n">
-        <v>9.062594385332057</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.690987696439243</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.100160867171385</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.095504041984897</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4.319754187646087</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3.688996192866707</v>
+      <c r="AP9" t="n">
+        <v>3.955497276736595</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>20.55364452126524</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25.38761339472948</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.062594385332101</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.690987696439235</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.100160867171407</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.095504041984878</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.319754187646045</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.68899619286669</v>
       </c>
     </row>
     <row r="10">
@@ -1466,106 +1901,151 @@
         <v>36</v>
       </c>
       <c r="B10" t="n">
+        <v>4.316525655048894</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.5844181192593596</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.607640735435347</v>
-      </c>
       <c r="D10" t="n">
-        <v>0.5954721559899777</v>
+        <v>3.015562923576817</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3104298509687092</v>
+        <v>0.6076407354353396</v>
       </c>
       <c r="F10" t="n">
-        <v>0.859249739859929</v>
+        <v>2.013920253334445</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6342685887806461</v>
+        <v>0.5954721559899691</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7321951378256855</v>
+        <v>1.239591213662928</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3914540469478567</v>
+        <v>0.3104298509687037</v>
       </c>
       <c r="J10" t="n">
-        <v>1.193583869444471</v>
+        <v>3.011913614422839</v>
       </c>
       <c r="K10" t="n">
-        <v>2.611136319258222</v>
+        <v>0.8592497398599275</v>
       </c>
       <c r="L10" t="n">
-        <v>1.789887488315823</v>
+        <v>2.919314728696931</v>
       </c>
       <c r="M10" t="n">
-        <v>1.632196000530513</v>
+        <v>0.6342685887806386</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3388503843468678</v>
+        <v>3.269436440230511</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29167190096899</v>
+        <v>0.7321951378256826</v>
       </c>
       <c r="P10" t="n">
-        <v>2.085085155434963</v>
+        <v>4.933464171665135</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.257412048248638</v>
+        <v>0.3914540469478633</v>
       </c>
       <c r="R10" t="n">
-        <v>19.76303770110768</v>
+        <v>5.275384014963049</v>
       </c>
       <c r="S10" t="n">
-        <v>24.98297028004773</v>
+        <v>1.193583869444467</v>
       </c>
       <c r="T10" t="n">
+        <v>8.878564434029668</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.611136319258219</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.221665544118181</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.78988748831583</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10.99791886808124</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.632196000530517</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.126800939730717</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.3388503843468518</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.156755057026165</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.291671900968975</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.38043721033655</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.085085155434951</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.90904606345359</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.6509482963005858</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="AG10" t="n">
+        <v>0.6509482963005855</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.8451597865424361</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>0.2518637393558536</v>
       </c>
-      <c r="X10" t="n">
-        <v>0.6799832005537306</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.2420786952952047</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AJ10" t="n">
+        <v>0.6799832005537315</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.2420786952952043</v>
+      </c>
+      <c r="AL10" t="n">
         <v>0.1306019477049387</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AM10" t="n">
         <v>0.1375747832342562</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AN10" t="n">
         <v>0.5543182893562961</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AO10" t="n">
         <v>0.04263982379562938</v>
       </c>
-      <c r="AD10" t="n">
-        <v>5.461427022733588</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.578890393442136</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.08866854490303</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.782662175052216</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.126920503858132</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.821864370853423</v>
+      <c r="AP10" t="n">
+        <v>9.257412048248664</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19.76303770110771</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>24.98297028004771</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.46142702273362</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.578890393442154</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.088668544902991</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.782662175052247</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.126920503858133</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.821864370853411</v>
       </c>
     </row>
     <row r="11">
@@ -1573,106 +2053,151 @@
         <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4902888978892634</v>
+        <v>4.050090259282852</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5272711341516559</v>
+        <v>0.4902888978892582</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6244966639486326</v>
+        <v>3.074469791712428</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2124581302203213</v>
+        <v>0.5272711341516609</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8799130629174153</v>
+        <v>2.120318351762637</v>
       </c>
       <c r="G11" t="n">
+        <v>0.6244966639486312</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.38214104290089</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2124581302203173</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.793651501026837</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8799130629174126</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.839454780687794</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.4212581593220389</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.4050131196688408</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6327827612943517</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.045163215544474</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.220680545489808</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3472616562684492</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.226115718190595</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.3340325980419009</v>
+        <v>3.288408394648362</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9574299818484279</v>
+        <v>0.4050131196688432</v>
       </c>
       <c r="P11" t="n">
-        <v>1.779581148539621</v>
+        <v>4.347449267636439</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.6039439876108</v>
+        <v>0.6327827612943548</v>
       </c>
       <c r="R11" t="n">
+        <v>5.080968380204106</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.045163215544478</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9.403023104272831</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.220680545489805</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.077766586307121</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.3472616562684503</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13.15330055735992</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.226115718190606</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.346854788198505</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3340325980419059</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.929429290724498</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.9574299818484202</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.88291603462346</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.779581148539613</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.329899275315089</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8031994346823051</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.6898757598580536</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.3682309455031664</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3075709040221308</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.8082290117604642</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1910017397551673</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.03012321619836886</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.1174000465738204</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.3010677875047008</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11.60394398761082</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>16.09853600263116</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AR11" t="n">
         <v>27.58694676263334</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.329899275315088</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.8031994346823055</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.6898757598580536</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.3682309455031664</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.30757090402213</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.8082290117604639</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.1910017397551673</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.03012321619836886</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.1174000465738204</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.3010677875047004</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.22072320764736</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.414743764358255</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>6.397876596650113</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>5.457940231406861</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.7061682897711457</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.665175720401482</v>
+      <c r="AS11" t="n">
+        <v>4.220723207647382</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.414743764358248</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.397876596650144</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.457940231406854</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.7061682897711303</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.665175720401472</v>
       </c>
     </row>
     <row r="12">
@@ -1680,106 +2205,151 @@
         <v>44</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3854013406225206</v>
+        <v>4.181825277160607</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5812818350553616</v>
+        <v>0.3854013406225216</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5661862425272034</v>
+        <v>3.028412208143421</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2004114870988</v>
+        <v>0.581281835055369</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6659072953269334</v>
+        <v>2.163862255286688</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2871059236463677</v>
+        <v>0.5661862425272041</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5027230767674514</v>
+        <v>1.149934285991766</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7771033557178574</v>
+        <v>0.2004114870988075</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7394119311004269</v>
+        <v>2.893852300571425</v>
       </c>
       <c r="K12" t="n">
-        <v>2.797603424415828</v>
+        <v>0.665907295326941</v>
       </c>
       <c r="L12" t="n">
-        <v>1.752856800625024</v>
+        <v>3.246582191667434</v>
       </c>
       <c r="M12" t="n">
-        <v>1.77091630701403</v>
+        <v>0.2871059236463707</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4653072192835299</v>
+        <v>3.686997539394084</v>
       </c>
       <c r="O12" t="n">
-        <v>1.044224851665458</v>
+        <v>0.5027230767674665</v>
       </c>
       <c r="P12" t="n">
-        <v>1.504690068591371</v>
+        <v>5.035687233117515</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.63632311264988</v>
+        <v>0.777103355717861</v>
       </c>
       <c r="R12" t="n">
-        <v>6.96776834350681</v>
+        <v>5.392392068391499</v>
       </c>
       <c r="S12" t="n">
-        <v>26.0096227242763</v>
+        <v>0.7394119311004292</v>
       </c>
       <c r="T12" t="n">
+        <v>9.49120834497721</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.797603424415826</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.529266373692783</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.752856800625017</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15.6149429622342</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.770916307014027</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.326491209598228</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.4653072192835408</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.50477913870524</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.044224851665459</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.277669372486</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.504690068591379</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.072774808070218</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.097473778406109</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AG12" t="n">
+        <v>1.09747377840611</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0.6739398626897729</v>
       </c>
-      <c r="W12" t="n">
-        <v>0.1946651816934032</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AI12" t="n">
+        <v>0.1946651816934029</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.9429830305361608</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0.5887138550036601</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AK12" t="n">
+        <v>0.5887138550036606</v>
+      </c>
+      <c r="AL12" t="n">
         <v>0.1751419489233658</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0.2165739378228634</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.2432911812024393</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.02157937876444539</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.592123635860974</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>5.647551034154692</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12.26790687399323</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.288971246412103</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8.269825688159285</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.328457070358744</v>
+      <c r="AM12" t="n">
+        <v>0.2165739378228635</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.2432911812024398</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.02157937876444514</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>17.63632311264995</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.967768343506779</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>26.00962272427626</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.59212363586093</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.647551034154707</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>12.26790687399321</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.288971246412075</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.269825688159258</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.328457070358718</v>
       </c>
     </row>
     <row r="13">
@@ -1787,106 +2357,151 @@
         <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4774366829119253</v>
+        <v>3.969890788861147</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6638080825299325</v>
+        <v>0.4774366829119309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5669208895036414</v>
+        <v>3.064885042162012</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1433972289529506</v>
+        <v>0.6638080825299262</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4933951096523206</v>
+        <v>1.852422819425485</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3073982197815697</v>
+        <v>0.5669208895036313</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3920946764274004</v>
+        <v>1.202556834756463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9164131752416586</v>
+        <v>0.1433972289529461</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7905373727224454</v>
+        <v>3.16180616168347</v>
       </c>
       <c r="K13" t="n">
-        <v>2.136559833999415</v>
+        <v>0.4933951096523231</v>
       </c>
       <c r="L13" t="n">
+        <v>3.306066160250925</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3073982197815622</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.619715024604402</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.392094676427396</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.696888261186849</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.9164131752416564</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.36975401542269</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7905373727224408</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.923284178429698</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.136559833999417</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.968740676729535</v>
+      </c>
+      <c r="W13" t="n">
         <v>3.654384289421712</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.219991489575905</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1309397129701186</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.062024916237512</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.8721584063858172</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>18.93095097487197</v>
-      </c>
-      <c r="R13" t="n">
-        <v>10.65924956915616</v>
-      </c>
-      <c r="S13" t="n">
-        <v>13.67532243579006</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
+        <v>16.82201765841814</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.219991489575895</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.397809154585582</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.130939712970116</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.495380092685208</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.062024916237511</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>16.64560649632423</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.8721584063858139</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.276580684448739</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.374222341507257</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.300586214311981</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.430434485915097</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AG13" t="n">
+        <v>1.374222341507258</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.3005862143119818</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.4304344859150971</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.8765214009014813</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AK13" t="n">
         <v>0.4131279929276475</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0.3081175462814964</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.1215457650335902</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.1438061049216156</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.1559217897263735</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>8.703807731052697</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>8.254946803881674</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12.14494606461662</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.840989748169865</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>10.01741774000162</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.482454514727646</v>
+      <c r="AL13" t="n">
+        <v>0.3081175462814971</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1215457650335906</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.1438061049216157</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1559217897263732</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18.93095097487192</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.65924956915612</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.67532243579011</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.703807731052684</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.254946803881653</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.14494606461658</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.840989748169837</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10.01741774000158</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.482454514727626</v>
       </c>
     </row>
     <row r="14">
@@ -1894,106 +2509,151 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3708123669345588</v>
+        <v>4.126824544675617</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4675491471250245</v>
+        <v>0.3708123669345509</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5171712798727335</v>
+        <v>3.170259861399208</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4146475424785724</v>
+        <v>0.4675491471250369</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4787817836076797</v>
+        <v>1.676242755141651</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2679363369576658</v>
+        <v>0.517171279872751</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4146866249264908</v>
+        <v>1.220693944427969</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6053850997576856</v>
+        <v>0.4146475424785709</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8158548994219392</v>
+        <v>3.420662346776098</v>
       </c>
       <c r="K14" t="n">
-        <v>1.221129050261375</v>
+        <v>0.4787817836076917</v>
       </c>
       <c r="L14" t="n">
-        <v>5.132331915945731</v>
+        <v>3.437238973234724</v>
       </c>
       <c r="M14" t="n">
-        <v>1.145915018563059</v>
+        <v>0.2679363369576664</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4756028732528521</v>
+        <v>3.849731185076597</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2457991762943429</v>
+        <v>0.4146866249265008</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2903934746283202</v>
+        <v>5.102857808053361</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.82513884430947</v>
+        <v>0.6053850997576858</v>
       </c>
       <c r="R14" t="n">
-        <v>17.90601814942258</v>
+        <v>5.820547619980013</v>
       </c>
       <c r="S14" t="n">
-        <v>8.823333380095553</v>
+        <v>0.8158548994219345</v>
       </c>
       <c r="T14" t="n">
+        <v>7.763908877382439</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.221129050261392</v>
+      </c>
+      <c r="V14" t="n">
+        <v>10.10704345196162</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.132331915945717</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16.48643527764949</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.145915018563047</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.918482029486666</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.4756028732528488</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.229037660177144</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.2457991762943502</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15.77833643647467</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.2903934746283244</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.9262096221881978</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AG14" t="n">
         <v>0.8478933779461363</v>
       </c>
-      <c r="V14" t="n">
-        <v>0.7396030107321993</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.400440226001646</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AH14" t="n">
+        <v>0.7396030107322001</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.4004402260016456</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>0.1893262408776087</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AK14" t="n">
         <v>0.2344937802517458</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0.4066013116231461</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.1479612738831122</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AL14" t="n">
+        <v>0.4066013116231468</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1479612738831123</v>
+      </c>
+      <c r="AN14" t="n">
         <v>0.4191098822906689</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0.3105609938166048</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>12.18717377628321</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>8.408827522648609</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10.78347571317743</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.05856498364758</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>4.39507054169232</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.686127270393356</v>
+      <c r="AO14" t="n">
+        <v>0.3105609938166045</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16.82513884430941</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>17.90601814942253</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.823333380095624</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12.18717377628322</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.408827522648583</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>10.78347571317745</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.058564983647565</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.395070541692354</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.686127270393347</v>
       </c>
     </row>
     <row r="15">
@@ -2001,106 +2661,151 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>0.559933741843208</v>
+        <v>4.356744778735354</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5981107697688349</v>
+        <v>0.5599337418431962</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6413248328861889</v>
+        <v>3.161400515662503</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5661398260035265</v>
+        <v>0.598110769768821</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3624784239129413</v>
+        <v>1.78454973875817</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3355389948007553</v>
+        <v>0.6413248328861965</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4926432684125319</v>
+        <v>1.326632221972621</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6844124461266621</v>
+        <v>0.5661398260035234</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4718611552068361</v>
+        <v>3.604089355796237</v>
       </c>
       <c r="K15" t="n">
-        <v>1.219954401642851</v>
+        <v>0.3624784239129377</v>
       </c>
       <c r="L15" t="n">
-        <v>5.370254248057805</v>
+        <v>3.780978933679483</v>
       </c>
       <c r="M15" t="n">
-        <v>1.250225102506723</v>
+        <v>0.3355389948007436</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2253766215684515</v>
+        <v>4.112747054380123</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6502545672173154</v>
+        <v>0.4926432684125275</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3177156069669608</v>
+        <v>5.531742605224662</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.192576021563113</v>
+        <v>0.6844124461266679</v>
       </c>
       <c r="R15" t="n">
-        <v>27.47414395809163</v>
+        <v>6.150581334466351</v>
       </c>
       <c r="S15" t="n">
-        <v>5.178726786280812</v>
+        <v>0.4718611552068381</v>
       </c>
       <c r="T15" t="n">
+        <v>7.546077040970055</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.219954401642849</v>
+      </c>
+      <c r="V15" t="n">
+        <v>11.28275272257162</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.370254248057802</v>
+      </c>
+      <c r="X15" t="n">
+        <v>15.19576495574342</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.250225102506727</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.041641410580702</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2253766215684629</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.346230842186864</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.650254567217314</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14.98293377519252</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.3177156069669661</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0.9637084514583173</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AG15" t="n">
         <v>0.3478586844493607</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AH15" t="n">
         <v>1.080584487690925</v>
       </c>
-      <c r="W15" t="n">
-        <v>0.3565091585144951</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AI15" t="n">
+        <v>0.3565091585144952</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.4661823320242096</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AK15" t="n">
         <v>0.05702426476398752</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AL15" t="n">
         <v>0.2121534780904686</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0.1613214133021793</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AM15" t="n">
+        <v>0.1613214133021797</v>
+      </c>
+      <c r="AN15" t="n">
         <v>0.5454240905234965</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AO15" t="n">
         <v>0.1703704500103486</v>
       </c>
-      <c r="AD15" t="n">
-        <v>14.79530605884299</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.332215412182859</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>8.60763548490881</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.857163471990918</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3.903970348656968</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.7592506878466033</v>
+      <c r="AP15" t="n">
+        <v>7.192576021563164</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>27.47414395809165</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.178726786280788</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>14.795306058843</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.332215412182889</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.60763548490884</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.857163471990929</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.903970348656991</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.759250687846621</v>
       </c>
     </row>
     <row r="16">
@@ -2108,106 +2813,151 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5486827653172512</v>
+        <v>4.46641406258822</v>
       </c>
       <c r="C16" t="n">
+        <v>0.5486827653172537</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.173758329250924</v>
+      </c>
+      <c r="E16" t="n">
         <v>1.009110753329355</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.6121546958720328</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.652956652749633</v>
-      </c>
       <c r="F16" t="n">
-        <v>0.6657952774789438</v>
+        <v>1.917261408152103</v>
       </c>
       <c r="G16" t="n">
-        <v>0.615202985688992</v>
+        <v>0.6121546958720445</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7382394196862295</v>
+        <v>1.608907274624859</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8675826393606597</v>
+        <v>0.6529566527496342</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6093540084098578</v>
+        <v>2.938276515060232</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8339366118162391</v>
+        <v>0.665795277478951</v>
       </c>
       <c r="L16" t="n">
-        <v>4.820375673994908</v>
+        <v>3.276819137983181</v>
       </c>
       <c r="M16" t="n">
-        <v>1.740227582035323</v>
+        <v>0.6152029856890012</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6279781081628542</v>
+        <v>3.665396918223944</v>
       </c>
       <c r="O16" t="n">
-        <v>1.051417634510692</v>
+        <v>0.7382394196862326</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8874279644841595</v>
+        <v>5.973250776893623</v>
       </c>
       <c r="Q16" t="n">
-        <v>17.37712049626379</v>
+        <v>0.8675826393606607</v>
       </c>
       <c r="R16" t="n">
-        <v>31.89104974555926</v>
+        <v>6.214365129935495</v>
       </c>
       <c r="S16" t="n">
-        <v>2.152684249531912</v>
+        <v>0.6093540084098631</v>
       </c>
       <c r="T16" t="n">
+        <v>6.984470113948605</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.8339366118162489</v>
+      </c>
+      <c r="V16" t="n">
+        <v>12.26610919942287</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.820375673994911</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.65165399556567</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.740227582035325</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.246562645976647</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6279781081628569</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.098179106228936</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.051417634510689</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14.20819913997243</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.8874279644841572</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.486742444002055</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AG16" t="n">
         <v>0.7191269985469491</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AH16" t="n">
         <v>0.6236665884221644</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AI16" t="n">
         <v>1.06876301742666</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AJ16" t="n">
         <v>0.1037831155880757</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AK16" t="n">
         <v>0.1289464304309592</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AL16" t="n">
         <v>0.1366742525468368</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AM16" t="n">
         <v>0.3334936010040004</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AN16" t="n">
         <v>0.2534128697966575</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AO16" t="n">
         <v>0.6814578649000022</v>
       </c>
-      <c r="AD16" t="n">
-        <v>9.110505613861788</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>5.754540980435846</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3.059800660110173</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>6.465659797570698</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.257225608154383</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.8523123194188406</v>
+      <c r="AP16" t="n">
+        <v>17.37712049626383</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>31.89104974555927</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.152684249531933</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.110505613861768</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.754540980435854</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.059800660110187</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.46565979757071</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.25722560815439</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.8523123194188459</v>
       </c>
     </row>
     <row r="17">
@@ -2215,106 +2965,151 @@
         <v>64</v>
       </c>
       <c r="B17" t="n">
-        <v>0.521453321733191</v>
+        <v>4.418062655482726</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9419488231278462</v>
+        <v>0.5214533217331905</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4059239541902923</v>
+        <v>3.505740139102876</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8141632107727077</v>
+        <v>0.941948823127847</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6917821758215652</v>
+        <v>1.519195684893135</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6170756612468009</v>
+        <v>0.4059239541902985</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8988487489654522</v>
+        <v>2.082527150890508</v>
       </c>
       <c r="I17" t="n">
-        <v>0.704888431954291</v>
+        <v>0.8141632107727088</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2558790996699229</v>
+        <v>3.85919532636886</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7572289958180765</v>
+        <v>0.6917821758215753</v>
       </c>
       <c r="L17" t="n">
-        <v>3.798492409092884</v>
+        <v>3.789587242514997</v>
       </c>
       <c r="M17" t="n">
-        <v>1.827220782940403</v>
+        <v>0.6170756612468055</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4636278405081974</v>
+        <v>4.34787810258571</v>
       </c>
       <c r="O17" t="n">
-        <v>1.030738912072729</v>
+        <v>0.8988487489654493</v>
       </c>
       <c r="P17" t="n">
-        <v>1.354661554549793</v>
+        <v>5.808369898084413</v>
       </c>
       <c r="Q17" t="n">
-        <v>23.18398038725533</v>
+        <v>0.7048884319542847</v>
       </c>
       <c r="R17" t="n">
-        <v>28.89550507343407</v>
+        <v>6.295086527618472</v>
       </c>
       <c r="S17" t="n">
-        <v>4.159753003034599</v>
+        <v>0.2558790996699201</v>
       </c>
       <c r="T17" t="n">
+        <v>7.379920672073547</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.7572289958180711</v>
+      </c>
+      <c r="V17" t="n">
+        <v>12.3038854789289</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.798492409092888</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12.27846078041577</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.827220782940401</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.632320428063416</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.4636278405082015</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.207426688135821</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.030738912072732</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22.3742577807948</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.354661554549796</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.36947835164761</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AG17" t="n">
         <v>0.5131083188227504</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AH17" t="n">
         <v>1.178428813308116</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AI17" t="n">
         <v>1.236006329536174</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AJ17" t="n">
         <v>0.2090318687231807</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AK17" t="n">
         <v>0.4099127980170227</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AL17" t="n">
         <v>0.7152319380637928</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AM17" t="n">
         <v>0.2060974175736886</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AN17" t="n">
         <v>0.919577915072573</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AO17" t="n">
         <v>0.7841604969036036</v>
       </c>
-      <c r="AD17" t="n">
-        <v>4.344835772454005</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>5.436916385815927</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>6.143471094709962</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>4.238227954620554</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.391068366338911</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.110569951816704</v>
+      <c r="AP17" t="n">
+        <v>23.18398038725532</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>28.8955050734341</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.15975300303461</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.344835772454009</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.436916385815906</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.143471094709952</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.23822795462057</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.391068366338931</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.110569951816721</v>
       </c>
     </row>
     <row r="18">
@@ -2322,106 +3117,151 @@
         <v>68</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7443229923424332</v>
+        <v>4.894812186466892</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8547813133378079</v>
+        <v>0.7443229923424289</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4382890626057791</v>
+        <v>3.93411723635054</v>
       </c>
       <c r="E18" t="n">
-        <v>1.278981623420685</v>
+        <v>0.8547813133378147</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9689238212895768</v>
+        <v>1.505715351665565</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7791838506410388</v>
+        <v>0.438289062605774</v>
       </c>
       <c r="H18" t="n">
-        <v>1.098993587415494</v>
+        <v>3.017127763966548</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9126330686051316</v>
+        <v>1.278981623420689</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7698401424933279</v>
+        <v>3.870276928445917</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6831479174133548</v>
+        <v>0.968923821289578</v>
       </c>
       <c r="L18" t="n">
-        <v>2.364774283701663</v>
+        <v>3.742316966857504</v>
       </c>
       <c r="M18" t="n">
-        <v>2.103631224193467</v>
+        <v>0.779183850641036</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7236971124133391</v>
+        <v>4.134434750041415</v>
       </c>
       <c r="O18" t="n">
-        <v>1.131453885638719</v>
+        <v>1.098993587415498</v>
       </c>
       <c r="P18" t="n">
-        <v>3.218831178989765</v>
+        <v>5.885144196157501</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.52085866814672</v>
+        <v>0.9126330686051356</v>
       </c>
       <c r="R18" t="n">
-        <v>22.6211851119708</v>
+        <v>6.388601824840756</v>
       </c>
       <c r="S18" t="n">
-        <v>3.91897711009043</v>
+        <v>0.7698401424933233</v>
       </c>
       <c r="T18" t="n">
+        <v>6.664360134184278</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6831479174133508</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10.57234261764886</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.364774283701671</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9.97105504576651</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.103631224193478</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.863738779258531</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.723697112413342</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.126834429551723</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.131453885638716</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>65.73143640988128</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.21883117898977</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2.481697573535076</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AG18" t="n">
         <v>0.2491145252501696</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AH18" t="n">
         <v>2.085048341372587</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AI18" t="n">
         <v>0.5795715039835975</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AJ18" t="n">
         <v>0.8523004914771729</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AK18" t="n">
         <v>0.2491154660119251</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AL18" t="n">
         <v>0.471762468100317</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AM18" t="n">
         <v>0.4180113184927976</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AN18" t="n">
         <v>1.329798647786559</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AO18" t="n">
         <v>0.2405617594462144</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.626393582833434</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>3.902427154300786</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.049568747055238</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.440313922442622</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.093423954603843</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.17572489927458</v>
+      <c r="AP18" t="n">
+        <v>22.52085866814677</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>22.62118511197082</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.918977110090436</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.626393582833421</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.902427154300808</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.049568747055254</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.440313922442624</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.09342395460386</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2.175724899274581</v>
       </c>
     </row>
     <row r="19">
@@ -2429,106 +3269,151 @@
         <v>72</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6498364663068315</v>
+        <v>5.250538629166615</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7125542221702708</v>
+        <v>0.6498364663068252</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6680641269254247</v>
+        <v>4.418875414379395</v>
       </c>
       <c r="E19" t="n">
-        <v>1.213937760583013</v>
+        <v>0.7125542221702614</v>
       </c>
       <c r="F19" t="n">
-        <v>1.232416628455544</v>
+        <v>3.131439973002838</v>
       </c>
       <c r="G19" t="n">
-        <v>0.981009506777727</v>
+        <v>0.6680641269254245</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8469949375228442</v>
+        <v>5.660231196882457</v>
       </c>
       <c r="I19" t="n">
-        <v>0.928277746544649</v>
+        <v>1.213937760583007</v>
       </c>
       <c r="J19" t="n">
-        <v>0.736352024705659</v>
+        <v>4.139545899263925</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7853740110533146</v>
+        <v>1.232416628455543</v>
       </c>
       <c r="L19" t="n">
-        <v>1.465130576989116</v>
+        <v>3.918974915537855</v>
       </c>
       <c r="M19" t="n">
-        <v>2.041428110666743</v>
+        <v>0.9810095067777124</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7127202500679606</v>
+        <v>4.33205217426671</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9179676403951653</v>
+        <v>0.8469949375228427</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6653929725833676</v>
+        <v>5.787656355343267</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.39495974010939</v>
+        <v>0.9282777465446514</v>
       </c>
       <c r="R19" t="n">
-        <v>15.23538759104632</v>
+        <v>5.9827453307044</v>
       </c>
       <c r="S19" t="n">
-        <v>4.215138778850449</v>
+        <v>0.7363520247056503</v>
       </c>
       <c r="T19" t="n">
+        <v>5.985733826666098</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.7853740110533158</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.693990273600594</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.465130576989117</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.7980485478355</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.041428110666749</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.998175416747429</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.7127202500679611</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.047838194248477</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.917967640395161</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>11.22814060387718</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.6653929725833669</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.385344271881463</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AG19" t="n">
         <v>0.3539142069748316</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AH19" t="n">
         <v>2.172410112765241</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AI19" t="n">
         <v>0.1690797450635561</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AJ19" t="n">
         <v>0.7008766699641463</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AK19" t="n">
         <v>0.08254534881064993</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AL19" t="n">
         <v>0.5937432908564059</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AM19" t="n">
         <v>0.2054387949333831</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AN19" t="n">
         <v>0.6977868790957716</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
         <v>0.7384552796794704</v>
       </c>
-      <c r="AD19" t="n">
-        <v>5.956976199837094</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>3.018943475382559</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>7.970545488333873</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.055595067658435</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.470066143373202</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.910783143218707</v>
+      <c r="AP19" t="n">
+        <v>19.39495974010942</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>15.23538759104629</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.215138778850477</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.956976199837109</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.018943475382572</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.970545488333869</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.0555950676584</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.470066143373196</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.910783143218736</v>
       </c>
     </row>
     <row r="20">
@@ -2536,106 +3421,151 @@
         <v>76</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8242948451779601</v>
+        <v>5.77140881125018</v>
       </c>
       <c r="C20" t="n">
+        <v>0.8242948451779485</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.018501116283973</v>
+      </c>
+      <c r="E20" t="n">
         <v>1.064941507441638</v>
       </c>
-      <c r="D20" t="n">
-        <v>1.13833718631618</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.754050898739867</v>
-      </c>
       <c r="F20" t="n">
-        <v>1.647595779033703</v>
+        <v>6.455296825839582</v>
       </c>
       <c r="G20" t="n">
-        <v>1.433621934010969</v>
+        <v>1.138337186316179</v>
       </c>
       <c r="H20" t="n">
-        <v>1.276588617316817</v>
+        <v>8.929296686139802</v>
       </c>
       <c r="I20" t="n">
-        <v>1.137507638003681</v>
+        <v>1.754050898739856</v>
       </c>
       <c r="J20" t="n">
-        <v>1.108905590648775</v>
+        <v>4.501593916229373</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8523708519084847</v>
+        <v>1.647595779033698</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7813155112454359</v>
+        <v>3.865434882369801</v>
       </c>
       <c r="M20" t="n">
-        <v>1.751825540123236</v>
+        <v>1.433621934010964</v>
       </c>
       <c r="N20" t="n">
-        <v>0.967114706215511</v>
+        <v>4.074476375052161</v>
       </c>
       <c r="O20" t="n">
-        <v>1.037178700769087</v>
+        <v>1.27658861731681</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6932703212771251</v>
+        <v>5.451171388216162</v>
       </c>
       <c r="Q20" t="n">
-        <v>15.14908815851751</v>
+        <v>1.13750763800368</v>
       </c>
       <c r="R20" t="n">
-        <v>12.44118104235695</v>
+        <v>5.332205580714843</v>
       </c>
       <c r="S20" t="n">
-        <v>2.268781238219669</v>
+        <v>1.10890559064877</v>
       </c>
       <c r="T20" t="n">
+        <v>5.484261305589714</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8523708519084834</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.977879662817521</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.7813155112454437</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.880030247487004</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.751825540123241</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.854143345294565</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.9671147062155112</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.039278947673293</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.037178700769092</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>10.57046521263601</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.6932703212771292</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2.11015668862343</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AG20" t="n">
         <v>0.7449806820541839</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AH20" t="n">
         <v>2.161161066132173</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AI20" t="n">
         <v>0.54597671064234</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AJ20" t="n">
         <v>0.687392398459411</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AK20" t="n">
         <v>0.08894444323237788</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AL20" t="n">
         <v>0.5455163198408446</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AM20" t="n">
         <v>0.199870934299786</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AN20" t="n">
         <v>0.4311595693154672</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AO20" t="n">
         <v>0.4583629559806865</v>
       </c>
-      <c r="AD20" t="n">
-        <v>8.588293517618732</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.921527157366012</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>6.970529970225164</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.156304241687642</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.857891426811769</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.199213085497328</v>
+      <c r="AP20" t="n">
+        <v>15.14908815851746</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12.44118104235694</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.268781238219691</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.588293517618741</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.921527157365978</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.970529970225168</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.15630424168765</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.857891426811803</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.199213085497309</v>
       </c>
     </row>
     <row r="21">
@@ -2643,106 +3573,151 @@
         <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4871178191516737</v>
+        <v>6.030982584094819</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7709985883177674</v>
+        <v>0.4871178191516696</v>
       </c>
       <c r="D21" t="n">
-        <v>1.725364926909757</v>
+        <v>5.473654188783676</v>
       </c>
       <c r="E21" t="n">
-        <v>1.862487684968331</v>
+        <v>0.7709985883177665</v>
       </c>
       <c r="F21" t="n">
-        <v>1.554264400484745</v>
+        <v>10.20534884932875</v>
       </c>
       <c r="G21" t="n">
-        <v>1.172361115672713</v>
+        <v>1.725364926909759</v>
       </c>
       <c r="H21" t="n">
-        <v>1.028737311428788</v>
+        <v>11.26938126086713</v>
       </c>
       <c r="I21" t="n">
-        <v>1.541481165052842</v>
+        <v>1.862487684968325</v>
       </c>
       <c r="J21" t="n">
-        <v>1.337018105374937</v>
+        <v>5.390285045405303</v>
       </c>
       <c r="K21" t="n">
-        <v>1.127665979888035</v>
+        <v>1.55426440048474</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3703873767575813</v>
+        <v>4.788877627824652</v>
       </c>
       <c r="M21" t="n">
-        <v>1.101365792377041</v>
+        <v>1.172361115672719</v>
       </c>
       <c r="N21" t="n">
+        <v>4.583062517215353</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.028737311428785</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.925642582385753</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.541481165052848</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5.04470707559854</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.337018105374948</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.014054001648867</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.127665979888034</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.250091624234674</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.3703873767575759</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.97348523971537</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.101365792377029</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.012076707857672</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.323931131595629</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.405097533518787</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.15966735733907</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>11.92288546360645</v>
-      </c>
-      <c r="R21" t="n">
-        <v>8.045017020638165</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.623654580110926</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="AB21" t="n">
+        <v>5.287239965182637</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.405097533518792</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10.10199032894175</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.159667357339067</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.907583877476318</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AG21" t="n">
         <v>0.6602333501576872</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AH21" t="n">
         <v>2.117340770856435</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AI21" t="n">
         <v>0.8612140221174523</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AJ21" t="n">
         <v>0.6705261763290461</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AK21" t="n">
         <v>0.3159645034311253</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AL21" t="n">
         <v>0.198274138174845</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AM21" t="n">
         <v>0.300198648230084</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AN21" t="n">
         <v>0.2841286882036668</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AO21" t="n">
         <v>0.2812659173259226</v>
       </c>
-      <c r="AD21" t="n">
-        <v>10.0601614141461</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>4.627921889220537</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>5.759773259095901</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.207268866186589</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.401463472132934</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.205481216634482</v>
+      <c r="AP21" t="n">
+        <v>11.92288546360644</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8.045017020638225</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.62365458011089</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10.06016141414609</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.627921889220528</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.759773259095899</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.207268866186626</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.401463472132916</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.205481216634508</v>
       </c>
     </row>
     <row r="22">
@@ -2750,106 +3725,151 @@
         <v>84</v>
       </c>
       <c r="B22" t="n">
-        <v>0.38941409354627</v>
+        <v>6.48609010516015</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6900194755597014</v>
+        <v>0.3894140935462733</v>
       </c>
       <c r="D22" t="n">
-        <v>2.158016428804334</v>
+        <v>6.134298227908312</v>
       </c>
       <c r="E22" t="n">
-        <v>1.797097773282918</v>
+        <v>0.6900194755596989</v>
       </c>
       <c r="F22" t="n">
-        <v>1.32983094870299</v>
+        <v>11.89736451120538</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9561738477886527</v>
+        <v>2.158016428804339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8128003783698063</v>
+        <v>11.57763971456477</v>
       </c>
       <c r="I22" t="n">
-        <v>1.479564795451445</v>
+        <v>1.797097773282921</v>
       </c>
       <c r="J22" t="n">
+        <v>6.057943811365464</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.32983094870298</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.545521964884277</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.9561738477886501</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.389231886675537</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8128003783697971</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.143964373680069</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.479564795451447</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.961973054536545</v>
+      </c>
+      <c r="S22" t="n">
         <v>1.239848605573912</v>
       </c>
-      <c r="K22" t="n">
-        <v>1.486344113701058</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.5997957842604308</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.4034589013220815</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.449461444309348</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.375043321302625</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.328500378441181</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>12.07434213082355</v>
-      </c>
-      <c r="R22" t="n">
-        <v>4.909147496583824</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5.710719951791734</v>
-      </c>
       <c r="T22" t="n">
+        <v>4.267525136836676</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.48634411370107</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.03564866824065</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.599795784260442</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.077420035016467</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.4034589013220753</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.88779272236268</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.449461444309359</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4.68729774371262</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.37504332130263</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>9.405192754017204</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.32850037844118</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.428890654390058</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AG22" t="n">
         <v>0.6780150686442741</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AH22" t="n">
         <v>1.946754344424065</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AI22" t="n">
         <v>0.7220113116270495</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AJ22" t="n">
         <v>0.6679385440895005</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AK22" t="n">
         <v>0.277642133521492</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AL22" t="n">
         <v>0.488863889250768</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AM22" t="n">
         <v>0.1989698097279805</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AN22" t="n">
         <v>0.4494581044320879</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
         <v>0.1313656465241988</v>
       </c>
-      <c r="AD22" t="n">
-        <v>10.12701547749535</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>3.697980606073336</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>5.632087961806391</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.650794161647268</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.036948247403021</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.061980170226564</v>
+      <c r="AP22" t="n">
+        <v>12.07434213082354</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4.90914749658374</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.710719951791763</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10.12701547749536</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.697980606073326</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.632087961806392</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.650794161647247</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.036948247403052</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.061980170226549</v>
       </c>
     </row>
     <row r="23">
@@ -2857,106 +3877,151 @@
         <v>88</v>
       </c>
       <c r="B23" t="n">
-        <v>0.349170643833274</v>
+        <v>6.875856887849877</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2610953876857289</v>
+        <v>0.3491706438332804</v>
       </c>
       <c r="D23" t="n">
-        <v>2.204261671449216</v>
+        <v>6.193557319551111</v>
       </c>
       <c r="E23" t="n">
-        <v>1.300753345422588</v>
+        <v>0.2610953876857213</v>
       </c>
       <c r="F23" t="n">
-        <v>1.470663039985951</v>
+        <v>14.56292881294896</v>
       </c>
       <c r="G23" t="n">
-        <v>0.798247513898978</v>
+        <v>2.204261671449228</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8023388317004262</v>
+        <v>12.82214672757095</v>
       </c>
       <c r="I23" t="n">
-        <v>1.221091920350833</v>
+        <v>1.300753345422583</v>
       </c>
       <c r="J23" t="n">
-        <v>1.125514019643679</v>
+        <v>6.910881183016442</v>
       </c>
       <c r="K23" t="n">
-        <v>1.529339216653239</v>
+        <v>1.470663039985942</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5197361900452637</v>
+        <v>6.238771369478711</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2176054090050508</v>
+        <v>0.7982475138989763</v>
       </c>
       <c r="N23" t="n">
-        <v>1.633509312253585</v>
+        <v>6.267544187334304</v>
       </c>
       <c r="O23" t="n">
-        <v>1.443169117098228</v>
+        <v>0.8023388317004309</v>
       </c>
       <c r="P23" t="n">
-        <v>1.554435922834361</v>
+        <v>4.815254632327296</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.50058819051975</v>
+        <v>1.221091920350842</v>
       </c>
       <c r="R23" t="n">
-        <v>6.820523875293429</v>
+        <v>4.304045426264706</v>
       </c>
       <c r="S23" t="n">
-        <v>4.558824838776757</v>
+        <v>1.125514019643684</v>
       </c>
       <c r="T23" t="n">
+        <v>3.685711754423264</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.529339216653247</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.357121807315126</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.5197361900452698</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.123458297535688</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.2176054090050559</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.55078395064406</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.633509312253599</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.280925249339453</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.443169117098239</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.692262773044131</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.55443592283437</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.5956814904495285</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AG23" t="n">
         <v>0.6671488027184125</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AH23" t="n">
         <v>0.9215997587543621</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AI23" t="n">
         <v>0.9646254910979638</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AJ23" t="n">
         <v>0.3291041982396758</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AK23" t="n">
         <v>0.3593592132278243</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AL23" t="n">
         <v>0.307978450139384</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AM23" t="n">
         <v>0.4191229110827411</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AN23" t="n">
         <v>0.3763761174446649</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AO23" t="n">
         <v>0.199755982491453</v>
       </c>
-      <c r="AD23" t="n">
-        <v>5.11565838279094</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>4.498010417642951</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.741240408092985</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.275289418976342</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.039534297681836</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.436035256187246</v>
+      <c r="AP23" t="n">
+        <v>13.50058819051978</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.82052387529339</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.558824838776779</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.115658382790965</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.498010417642961</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.741240408092986</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.275289418976339</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.039534297681795</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.436035256187218</v>
       </c>
     </row>
     <row r="24">
@@ -2964,106 +4029,151 @@
         <v>92</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4377099211496475</v>
+        <v>6.684722737212395</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2163669188186821</v>
+        <v>0.4377099211496354</v>
       </c>
       <c r="D24" t="n">
-        <v>1.669877441153655</v>
+        <v>6.532268043876761</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9487197003664221</v>
+        <v>0.216366918818692</v>
       </c>
       <c r="F24" t="n">
+        <v>15.90742825711099</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.669877441153654</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14.00555861807763</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9487197003664246</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7.466708535627773</v>
+      </c>
+      <c r="K24" t="n">
         <v>1.810143038017119</v>
       </c>
-      <c r="G24" t="n">
+      <c r="L24" t="n">
+        <v>6.985205477815044</v>
+      </c>
+      <c r="M24" t="n">
         <v>0.8893424997566207</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.5234853421762857</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.9785969395449773</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.8883613471895032</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.738529530827133</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.7229814055181981</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.4105754323972528</v>
-      </c>
       <c r="N24" t="n">
-        <v>1.764139694402997</v>
+        <v>6.599072901498645</v>
       </c>
       <c r="O24" t="n">
-        <v>1.677467454236149</v>
+        <v>0.5234853421762891</v>
       </c>
       <c r="P24" t="n">
-        <v>1.334290848233338</v>
+        <v>5.376997341488983</v>
       </c>
       <c r="Q24" t="n">
-        <v>15.31234807466609</v>
+        <v>0.9785969395449728</v>
       </c>
       <c r="R24" t="n">
-        <v>6.099590634894676</v>
+        <v>4.888780801884264</v>
       </c>
       <c r="S24" t="n">
-        <v>7.438889428945051</v>
+        <v>0.8883613471894934</v>
       </c>
       <c r="T24" t="n">
+        <v>3.694062848732874</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.738529530827123</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.192715594657043</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.7229814055181919</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.9332895264751199</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.410575432397261</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.775119355154452</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.764139694403003</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.633738231650201</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.677467454236137</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>7.765394288640257</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.334290848233337</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0.1359396829371441</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AG24" t="n">
         <v>0.2999414391081784</v>
       </c>
-      <c r="V24" t="n">
+      <c r="AH24" t="n">
         <v>0.02910435693931104</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AI24" t="n">
         <v>0.4755416853740922</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AJ24" t="n">
         <v>0.1528144841710715</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AK24" t="n">
         <v>0.1920384531380209</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AL24" t="n">
         <v>0.3969361723442259</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AM24" t="n">
         <v>0.2852550843204731</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AN24" t="n">
         <v>0.16580994650401</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AO24" t="n">
         <v>0.3417432850501428</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.285113420543172</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.255823697655043</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.9188633052429918</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.094449612244539</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.412684952935614</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.315394129167791</v>
+      <c r="AP24" t="n">
+        <v>15.31234807466614</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.09959063489471</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>7.438889428945023</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.285113420543147</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.255823697655071</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.9188633052429855</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.094449612244554</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.412684952935589</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.315394129167794</v>
       </c>
     </row>
     <row r="25">
@@ -3071,106 +4181,151 @@
         <v>96</v>
       </c>
       <c r="B25" t="n">
-        <v>0.4008814325836604</v>
+        <v>6.920393642197516</v>
       </c>
       <c r="C25" t="n">
-        <v>0.130508527764265</v>
+        <v>0.4008814325836527</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8768043742765019</v>
+        <v>6.676421228107297</v>
       </c>
       <c r="E25" t="n">
-        <v>1.254401318314941</v>
+        <v>0.130508527764258</v>
       </c>
       <c r="F25" t="n">
-        <v>2.080696300996824</v>
+        <v>17.21184205807362</v>
       </c>
       <c r="G25" t="n">
-        <v>1.158278093977778</v>
+        <v>0.8768043742765018</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7545295781820365</v>
+        <v>14.20718425727972</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8292265350792701</v>
+        <v>1.254401318314948</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7240896902318122</v>
+        <v>7.924149490853649</v>
       </c>
       <c r="K25" t="n">
-        <v>1.72512085750316</v>
+        <v>2.080696300996827</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8266875898468452</v>
+        <v>7.570824785359208</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7699488396579086</v>
+        <v>1.158278093977782</v>
       </c>
       <c r="N25" t="n">
-        <v>2.039950929499089</v>
+        <v>7.142618039890833</v>
       </c>
       <c r="O25" t="n">
-        <v>1.941148170281004</v>
+        <v>0.7545295781820432</v>
       </c>
       <c r="P25" t="n">
-        <v>1.254298642152393</v>
+        <v>5.105860584954168</v>
       </c>
       <c r="Q25" t="n">
-        <v>16.04980874153884</v>
+        <v>0.8292265350792696</v>
       </c>
       <c r="R25" t="n">
-        <v>5.624083687766136</v>
+        <v>5.09305482785806</v>
       </c>
       <c r="S25" t="n">
+        <v>0.724089690231815</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.803212720745984</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.725120857503163</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.324220524800676</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.8266875898468357</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.9174109325456358</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.7699488396579072</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.889327474641749</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.03995092949909</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.28298568027046</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.941148170281</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>8.193944932541065</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.254298642152389</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.1913752855432173</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.036789704852279</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.1771962755525102</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.1662583512546972</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.1213800990149936</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.2129433897854838</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.2781675058361054</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.17591922279601</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.3174869480196399</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.2800854118780186</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>16.04980874153882</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5.624083687766076</v>
+      </c>
+      <c r="AR25" t="n">
         <v>10.87674132907614</v>
       </c>
-      <c r="T25" t="n">
-        <v>0.1913752855432173</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.036789704852279</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.1771962755525102</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.1662583512546972</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.1213800990149936</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.2129433897854838</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.2781675058361054</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.17591922279601</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.3174869480196399</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.2800854118780186</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.392070649281795</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.253007084583917</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.450452625833462</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.634293990299556</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.626613847480893</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.48331479959531</v>
+      <c r="AS25" t="n">
+        <v>2.392070649281772</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.253007084583872</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.450452625833492</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.6342939902995555</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.626613847480914</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.483314799595302</v>
       </c>
     </row>
     <row r="26">
@@ -3178,106 +4333,151 @@
         <v>100</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2463085396257432</v>
+        <v>7.010989599185284</v>
       </c>
       <c r="C26" t="n">
-        <v>0.134585837109516</v>
+        <v>0.2463085396257339</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7045262054770229</v>
+        <v>6.610144947322754</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9855041231247201</v>
+        <v>0.134585837109506</v>
       </c>
       <c r="F26" t="n">
-        <v>2.737457371680496</v>
+        <v>16.35267266095297</v>
       </c>
       <c r="G26" t="n">
-        <v>1.031790428861677</v>
+        <v>0.7045262054770237</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7452469444247776</v>
+        <v>13.10893654655218</v>
       </c>
       <c r="I26" t="n">
-        <v>1.035879098797855</v>
+        <v>0.9855041231247286</v>
       </c>
       <c r="J26" t="n">
-        <v>1.22731525802904</v>
+        <v>8.448283564248021</v>
       </c>
       <c r="K26" t="n">
-        <v>1.539094608691011</v>
+        <v>2.7374573716805</v>
       </c>
       <c r="L26" t="n">
-        <v>1.182203222575138</v>
+        <v>8.146927717129369</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9502962810561929</v>
+        <v>1.031790428861687</v>
       </c>
       <c r="N26" t="n">
-        <v>2.160390548887761</v>
+        <v>7.708908164548041</v>
       </c>
       <c r="O26" t="n">
-        <v>2.558060609187177</v>
+        <v>0.7452469444247759</v>
       </c>
       <c r="P26" t="n">
-        <v>1.839267807660746</v>
+        <v>5.392559963128676</v>
       </c>
       <c r="Q26" t="n">
-        <v>14.08196861606215</v>
+        <v>1.035879098797851</v>
       </c>
       <c r="R26" t="n">
-        <v>4.558085438802213</v>
+        <v>5.187887257529889</v>
       </c>
       <c r="S26" t="n">
-        <v>11.54916066869539</v>
+        <v>1.227315258029039</v>
       </c>
       <c r="T26" t="n">
+        <v>3.643062186065542</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.539094608691012</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.277753026224854</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.18220322257513</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.796966769852693</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.9502962810561866</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.263941906675962</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.160390548887745</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.630804717525439</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.558060609187175</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>8.428473026307959</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.839267807660742</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0.1244365694223319</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AG26" t="n">
         <v>0.1808043858260745</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AH26" t="n">
         <v>0.3125872615178365</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AI26" t="n">
         <v>0.1657006481492388</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AJ26" t="n">
         <v>0.2754118907318148</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AK26" t="n">
         <v>0.1711495271484604</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AL26" t="n">
         <v>0.2345580259307551</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AM26" t="n">
         <v>0.06268986485914853</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AN26" t="n">
         <v>0.5398785786655238</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AO26" t="n">
         <v>0.3076815330235873</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.704795562587061</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.678594072454639</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.17965267365323</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.7292408561315341</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.911789854873427</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.539651363856034</v>
+      <c r="AP26" t="n">
+        <v>14.08196861606216</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.558085438802189</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11.5491606686954</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.704795562587</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.678594072454579</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.179652673653229</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.7292408561315029</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.911789854873468</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.53965136385604</v>
       </c>
     </row>
   </sheetData>
